--- a/top_200_players_five_leagues.xlsx
+++ b/top_200_players_five_leagues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daven.Argile\Documents\fifa-5aside-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{45A194B3-4FA2-4486-A60A-259E6DE487C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{02798220-822D-409B-ADD7-CD4706AF0EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -19451,14 +19451,14 @@
         <v>93</v>
       </c>
       <c r="G88" s="33">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H88" s="33">
         <v>88</v>
       </c>
       <c r="I88" s="34">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J88" s="31" t="s">
         <v>800</v>

--- a/top_200_players_five_leagues.xlsx
+++ b/top_200_players_five_leagues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daven.Argile\Documents\fifa-5aside-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{693676F2-3CB7-4ECC-93F5-74C23501A1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{166591C3-A970-420C-86F1-D2E737899C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -8295,9 +8295,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PremierLeagueTop200" displayName="PremierLeagueTop200" ref="A1:J201">
   <autoFilter ref="A1:J201" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J201">
-    <sortCondition descending="1" ref="I1:I201"/>
-  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Player"/>
@@ -8317,9 +8314,6 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LaLigaTop200" displayName="LaLigaTop200" ref="A1:J201">
   <autoFilter ref="A1:J201" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J201">
-    <sortCondition descending="1" ref="I1:I201"/>
-  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Player"/>
@@ -8339,9 +8333,6 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="SerieATop200" displayName="SerieATop200" ref="A1:J201">
   <autoFilter ref="A1:J201" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J201">
-    <sortCondition descending="1" ref="I1:I201"/>
-  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Player"/>
@@ -8361,9 +8352,6 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Ligue1Top200" displayName="Ligue1Top200" ref="A1:J201">
   <autoFilter ref="A1:J201" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J201">
-    <sortCondition descending="1" ref="I1:I201"/>
-  </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Rank"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Player"/>
@@ -45289,11 +45277,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K199" xr:uid="{00000000-0001-0000-0500-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K199">
-      <sortCondition descending="1" ref="I1:I199"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:K199" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
